--- a/考点导入模板.xlsx
+++ b/考点导入模板.xlsx
@@ -434,14 +434,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -452,20 +450,10 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>模式</t>
+          <t>正面（问题）</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>题型</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>正面（问题）</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>反面（答案）</t>
         </is>
@@ -482,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -516,118 +504,106 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>模式</t>
+          <t>正面（问题）</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>填写：复习（考前复习重点）/ 学习（详细学习内容），不填默认为「复习」</t>
+          <t>记忆卡片正面显示的文字</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>题型</t>
+          <t>反面（答案）</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>填写：单选 / 多选 / 判断</t>
+          <t>记忆卡片反面显示的文字（可含解析、提示等）</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>正面（问题）</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>记忆卡片正面显示的文字</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>反面（答案）</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>记忆卡片反面显示的文字</t>
-        </is>
-      </c>
+          <t>注意事项</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>章节名称必须与 index.html 中的章节名称完全一致，否则无法正确导入</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>注意事项</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>导论 对应网页中的「导论」章节</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>章节名称必须与 index.html 中的章节名称完全一致，否则无法正确导入</t>
+          <t>运行导入脚本时会让你选择模式：重点复习 / 学习模式</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>模式列填写「复习」或「学习」，决定卡片进入哪个数据集</t>
+          <t>也可以用命令行参数直接指定模式：python3 导入脚本.py --mode review</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>每次填写完一个章节的内容后，运行导入脚本即可自动写入网页</t>
+          <t>可以多次导入，新内容会追加，不会覆盖已有内容</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
-        <is>
-          <t>可以多次导入，新内容会追加到对应模式，不会删除已有内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
         <is>
           <t>建议先填少量内容测试，确认格式正确后再批量填写</t>
         </is>
